--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXI/LTAIPT_A63F21B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXI/LTAIPT_A63F21B.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="88">
   <si>
     <t>48971</t>
   </si>
@@ -114,42 +114,33 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>9CB852D56A0CE09E72A02064D029DA7C</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
-  </si>
-  <si>
-    <t>4867677</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Depto.%20de%20Programacion%20y%20Presupuesto/4to_Trimestre/Informacion%20Presupuestal/prsupuestal_4to_trimestre.pdf</t>
+    <t>C226142918D4AA9678F79D5E3945406D</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
+  </si>
+  <si>
+    <t>6391610</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/1er%20Trimestre/Informacion%20Presupuestal/Informacion%20Presupuestal.pdf</t>
   </si>
   <si>
     <t>Departamento de Programación y Presupuesto</t>
   </si>
   <si>
-    <t>13/01/2023</t>
+    <t>25/04/2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>4503122</t>
-  </si>
-  <si>
-    <t>3001844</t>
-  </si>
-  <si>
-    <t>2437909</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -204,7 +195,7 @@
     <t>Subejercicio</t>
   </si>
   <si>
-    <t>BD533A7E70A97C7A60A633470B623108</t>
+    <t>E9A4CE1D7739C4DDD2FE3AE639708194</t>
   </si>
   <si>
     <t>1000</t>
@@ -213,19 +204,19 @@
     <t>Servicios personales</t>
   </si>
   <si>
-    <t>482935413</t>
-  </si>
-  <si>
-    <t>8726840.17</t>
-  </si>
-  <si>
-    <t>491662253.17</t>
+    <t>501206101</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>A0A203CAF35F31C62B8199CF2266C350</t>
+    <t>85645506.28</t>
+  </si>
+  <si>
+    <t>415560594.7</t>
+  </si>
+  <si>
+    <t>2CF20E36FEEF52AEC534E780175BED03</t>
   </si>
   <si>
     <t>2000</t>
@@ -234,16 +225,16 @@
     <t>Materiales y suministros</t>
   </si>
   <si>
-    <t>8968534</t>
-  </si>
-  <si>
-    <t>52115.72</t>
-  </si>
-  <si>
-    <t>9020649.72</t>
-  </si>
-  <si>
-    <t>A0A203CAF35F31C624488D796F25C224</t>
+    <t>9112031</t>
+  </si>
+  <si>
+    <t>762952.45</t>
+  </si>
+  <si>
+    <t>8349078.55</t>
+  </si>
+  <si>
+    <t>2CF20E36FEEF52AECC40B12AC7E81564</t>
   </si>
   <si>
     <t>3000</t>
@@ -252,22 +243,16 @@
     <t>Servicios generales</t>
   </si>
   <si>
-    <t>44664539</t>
-  </si>
-  <si>
-    <t>-6295516.86</t>
-  </si>
-  <si>
-    <t>38369022.14</t>
-  </si>
-  <si>
-    <t>35088873.34</t>
-  </si>
-  <si>
-    <t>3280148.8</t>
-  </si>
-  <si>
-    <t>A0A203CAF35F31C6648DCA050F5E1007</t>
+    <t>44875950</t>
+  </si>
+  <si>
+    <t>3492570.77</t>
+  </si>
+  <si>
+    <t>41383379.23</t>
+  </si>
+  <si>
+    <t>2CF20E36FEEF52AE77C9DB1AECF7AAA5</t>
   </si>
   <si>
     <t>4000</t>
@@ -279,13 +264,7 @@
     <t>1400000</t>
   </si>
   <si>
-    <t>-369438.26</t>
-  </si>
-  <si>
-    <t>1030561.74</t>
-  </si>
-  <si>
-    <t>A0A203CAF35F31C670F4991B8799BEEA</t>
+    <t>2CF20E36FEEF52AE02CCA7754F25B3FC</t>
   </si>
   <si>
     <t>5000</t>
@@ -294,214 +273,13 @@
     <t>Bienes muebles e inmuebles</t>
   </si>
   <si>
-    <t>5786730</t>
-  </si>
-  <si>
-    <t>8091947.27</t>
-  </si>
-  <si>
-    <t>13878677.27</t>
-  </si>
-  <si>
-    <t>13874480.47</t>
-  </si>
-  <si>
-    <t>4196.8</t>
-  </si>
-  <si>
-    <t>0AE1BFE47FA26DED663FF2749B0982B7</t>
-  </si>
-  <si>
-    <t>338378653.9</t>
-  </si>
-  <si>
-    <t>144556759.1</t>
-  </si>
-  <si>
-    <t>DFB07FE7D5B7B5CDA1E3209C50A48C88</t>
-  </si>
-  <si>
-    <t>408781.7</t>
-  </si>
-  <si>
-    <t>9377315.7</t>
-  </si>
-  <si>
-    <t>4423759.12</t>
-  </si>
-  <si>
-    <t>4953556.58</t>
-  </si>
-  <si>
-    <t>A043CF06B5A092613ADB765328ADFD4A</t>
-  </si>
-  <si>
-    <t>4699076.43</t>
-  </si>
-  <si>
-    <t>49363615.43</t>
-  </si>
-  <si>
-    <t>17928846</t>
-  </si>
-  <si>
-    <t>31434769.43</t>
-  </si>
-  <si>
-    <t>57C9B2FF84545207318FE0A5E54D63B4</t>
-  </si>
-  <si>
-    <t>-422075.7</t>
-  </si>
-  <si>
-    <t>977924.3</t>
-  </si>
-  <si>
-    <t>889849.74</t>
-  </si>
-  <si>
-    <t>88074.56</t>
-  </si>
-  <si>
-    <t>59B9BD933FAFCAA9CEBF62B75EA6873B</t>
-  </si>
-  <si>
-    <t>2000000</t>
-  </si>
-  <si>
-    <t>7786730</t>
-  </si>
-  <si>
-    <t>1629050.67</t>
-  </si>
-  <si>
-    <t>6157679.33</t>
-  </si>
-  <si>
-    <t>63A2FE5FD9522D6FB8E28FA354E7E7A6</t>
-  </si>
-  <si>
-    <t>232682170.69</t>
-  </si>
-  <si>
-    <t>250253242.31</t>
-  </si>
-  <si>
-    <t>5B0DBB30C741ED1E3347A633850121AB</t>
-  </si>
-  <si>
-    <t>-376708.72</t>
-  </si>
-  <si>
-    <t>9345242.72</t>
-  </si>
-  <si>
-    <t>3550940.09</t>
-  </si>
-  <si>
-    <t>5794302.63</t>
-  </si>
-  <si>
-    <t>54FDBED7DDEFB3C3609544A5DE374037</t>
-  </si>
-  <si>
-    <t>3139183.4</t>
-  </si>
-  <si>
-    <t>47803722.4</t>
-  </si>
-  <si>
-    <t>10362766.26</t>
-  </si>
-  <si>
-    <t>37440956.14</t>
-  </si>
-  <si>
-    <t>3457B9738C44871F5A0AF055A484000A</t>
-  </si>
-  <si>
-    <t>376708.72</t>
-  </si>
-  <si>
-    <t>1023291.28</t>
-  </si>
-  <si>
-    <t>587114.54</t>
-  </si>
-  <si>
-    <t>436176.74</t>
-  </si>
-  <si>
-    <t>4BE97B72C70B4B91C49ADC21AE3951D9</t>
-  </si>
-  <si>
-    <t>261076.48</t>
-  </si>
-  <si>
-    <t>7525653.52</t>
-  </si>
-  <si>
-    <t>F7E0DD39FB14F64CB390BCCD34F2256E</t>
-  </si>
-  <si>
-    <t>87303753</t>
-  </si>
-  <si>
-    <t>395631660</t>
-  </si>
-  <si>
-    <t>322C0963DE76AD61E58638D1903919FF</t>
-  </si>
-  <si>
-    <t>50479</t>
-  </si>
-  <si>
-    <t>9019013</t>
-  </si>
-  <si>
-    <t>1163821</t>
-  </si>
-  <si>
-    <t>7855192</t>
-  </si>
-  <si>
-    <t>66EF899E596530698F737BC08FF8F451</t>
-  </si>
-  <si>
-    <t>1778799</t>
-  </si>
-  <si>
-    <t>46443338</t>
-  </si>
-  <si>
-    <t>3873119</t>
-  </si>
-  <si>
-    <t>42570218</t>
-  </si>
-  <si>
-    <t>774D82F05C090B9FB9032D3C8E46EAB5</t>
-  </si>
-  <si>
-    <t>-50479</t>
-  </si>
-  <si>
-    <t>1349521</t>
-  </si>
-  <si>
-    <t>19013</t>
-  </si>
-  <si>
-    <t>1330509</t>
-  </si>
-  <si>
-    <t>F6D8E3F83C76B614E60D70FEAE15E8CC</t>
-  </si>
-  <si>
-    <t>215676</t>
-  </si>
-  <si>
-    <t>7571054</t>
+    <t>8093964</t>
+  </si>
+  <si>
+    <t>69164.06</t>
+  </si>
+  <si>
+    <t>8024799.94</t>
   </si>
 </sst>
 </file>
@@ -900,12 +678,12 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="70.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="255" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="169" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
@@ -1098,16 +876,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="46.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1119,78 +899,78 @@
         <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" t="s">
         <v>45</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>46</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>47</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>48</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>49</v>
-      </c>
-      <c r="H2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1198,31 +978,31 @@
         <v>36</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="I4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1230,31 +1010,31 @@
         <v>36</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="F5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="I5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1262,31 +1042,31 @@
         <v>36</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="F6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="I6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1294,31 +1074,31 @@
         <v>36</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1326,511 +1106,31 @@
         <v>36</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
